--- a/REACT-KHACHSAN-VT/public/templates/template-export-excel-thong-ke-phong-da-ban.xlsx
+++ b/REACT-KHACHSAN-VT/public/templates/template-export-excel-thong-ke-phong-da-ban.xlsx
@@ -5,20 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CVK-18-04-26\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\FE-QUANLY-KHACHSAN-VT\REACT-KHACHSAN-VT\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BD3B0B-9E4B-4AFE-A5FC-D0DE462E71E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C024809E-AC67-4B89-958D-0ECCA60FC18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="2240" windowWidth="28800" windowHeight="15290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="7" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filter 1" guid="{D50BC7C8-DE49-44F4-AD72-F6A00FB1B283}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filter 2" guid="{F7DC3643-78E7-4146-8513-31BC859B9B43}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filter 1" guid="{D50BC7C8-DE49-44F4-AD72-F6A00FB1B283}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -341,7 +341,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -412,12 +412,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -497,22 +510,37 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -545,15 +573,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>235322</xdr:colOff>
+      <xdr:colOff>250544</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>134471</xdr:rowOff>
+      <xdr:rowOff>112060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>38007</xdr:colOff>
+      <xdr:colOff>54816</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>629453</xdr:rowOff>
+      <xdr:rowOff>607042</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -582,8 +610,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="235322" y="134471"/>
-          <a:ext cx="2413656" cy="494982"/>
+          <a:off x="250544" y="112060"/>
+          <a:ext cx="2527301" cy="494982"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -804,42 +832,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
     </row>
     <row r="2" spans="1:34" s="5" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
@@ -944,7 +972,7 @@
       </c>
     </row>
     <row r="3" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="29" t="s">
         <v>39</v>
       </c>
       <c r="B3" s="21" t="s">
@@ -986,10 +1014,10 @@
       <c r="AE3" s="16"/>
       <c r="AF3" s="16"/>
       <c r="AG3" s="17"/>
-      <c r="AH3" s="28"/>
+      <c r="AH3" s="33"/>
     </row>
     <row r="4" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
+      <c r="A4" s="29"/>
       <c r="B4" s="21" t="s">
         <v>26</v>
       </c>
@@ -1002,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="18">
-        <f t="shared" ref="E4:AG4" si="0">E3/80</f>
+        <f t="shared" ref="E4:AH4" si="0">E3/80</f>
         <v>0</v>
       </c>
       <c r="F4" s="18">
@@ -1117,10 +1145,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH4" s="28"/>
+      <c r="AH4" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:34" s="19" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="29" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="24" t="s">
@@ -1162,10 +1193,10 @@
       <c r="AE5" s="10"/>
       <c r="AF5" s="10"/>
       <c r="AG5" s="10"/>
-      <c r="AH5" s="10"/>
+      <c r="AH5" s="34"/>
     </row>
     <row r="6" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="27"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="21" t="s">
         <v>26</v>
       </c>
@@ -1293,13 +1324,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH6" s="11">
-        <f>AH5/80</f>
-        <v>0</v>
-      </c>
+      <c r="AH6" s="35"/>
     </row>
     <row r="7" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="29" t="s">
         <v>41</v>
       </c>
       <c r="B7" s="21" t="s">
@@ -1341,10 +1369,10 @@
       <c r="AE7" s="16"/>
       <c r="AF7" s="16"/>
       <c r="AG7" s="17"/>
-      <c r="AH7" s="28"/>
+      <c r="AH7" s="33"/>
     </row>
     <row r="8" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="21" t="s">
         <v>26</v>
       </c>
@@ -1357,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="18">
-        <f t="shared" ref="E8:AG8" si="2">E7/80</f>
+        <f t="shared" ref="E8:AH8" si="2">E7/80</f>
         <v>0</v>
       </c>
       <c r="F8" s="18">
@@ -1472,10 +1500,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AH8" s="28"/>
+      <c r="AH8" s="18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:34" s="19" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="29" t="s">
         <v>42</v>
       </c>
       <c r="B9" s="24" t="s">
@@ -1517,10 +1548,10 @@
       <c r="AE9" s="10"/>
       <c r="AF9" s="10"/>
       <c r="AG9" s="10"/>
-      <c r="AH9" s="10"/>
+      <c r="AH9" s="36"/>
     </row>
     <row r="10" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="21" t="s">
         <v>26</v>
       </c>
@@ -1648,13 +1679,10 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AH10" s="11">
-        <f>AH9/80</f>
-        <v>0</v>
-      </c>
+      <c r="AH10" s="37"/>
     </row>
     <row r="11" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="29" t="s">
         <v>43</v>
       </c>
       <c r="B11" s="21" t="s">
@@ -1696,10 +1724,10 @@
       <c r="AE11" s="16"/>
       <c r="AF11" s="16"/>
       <c r="AG11" s="17"/>
-      <c r="AH11" s="28"/>
+      <c r="AH11" s="33"/>
     </row>
     <row r="12" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
+      <c r="A12" s="29"/>
       <c r="B12" s="21" t="s">
         <v>26</v>
       </c>
@@ -1712,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="18">
-        <f t="shared" ref="E12:AG12" si="4">E11/80</f>
+        <f t="shared" ref="E12:AH12" si="4">E11/80</f>
         <v>0</v>
       </c>
       <c r="F12" s="18">
@@ -1827,10 +1855,13 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AH12" s="28"/>
+      <c r="AH12" s="18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:34" s="19" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="29" t="s">
         <v>0</v>
       </c>
       <c r="B13" s="24" t="s">
@@ -1872,10 +1903,10 @@
       <c r="AE13" s="10"/>
       <c r="AF13" s="10"/>
       <c r="AG13" s="10"/>
-      <c r="AH13" s="10"/>
+      <c r="AH13" s="36"/>
     </row>
     <row r="14" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="27"/>
+      <c r="A14" s="29"/>
       <c r="B14" s="21" t="s">
         <v>26</v>
       </c>
@@ -2003,13 +2034,10 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH14" s="11">
-        <f>AH13/80</f>
-        <v>0</v>
-      </c>
+      <c r="AH14" s="37"/>
     </row>
     <row r="15" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="29" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="21" t="s">
@@ -2051,10 +2079,10 @@
       <c r="AE15" s="16"/>
       <c r="AF15" s="16"/>
       <c r="AG15" s="17"/>
-      <c r="AH15" s="28"/>
+      <c r="AH15" s="33"/>
     </row>
     <row r="16" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="27"/>
+      <c r="A16" s="29"/>
       <c r="B16" s="21" t="s">
         <v>26</v>
       </c>
@@ -2067,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="18">
-        <f t="shared" ref="E16:AG16" si="6">E15/80</f>
+        <f t="shared" ref="E16:AH16" si="6">E15/80</f>
         <v>0</v>
       </c>
       <c r="F16" s="18">
@@ -2182,10 +2210,13 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AH16" s="28"/>
+      <c r="AH16" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:34" s="19" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="29" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="24" t="s">
@@ -2230,7 +2261,7 @@
       <c r="AH17" s="10"/>
     </row>
     <row r="18" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="27"/>
+      <c r="A18" s="29"/>
       <c r="B18" s="21" t="s">
         <v>26</v>
       </c>
@@ -2364,7 +2395,7 @@
       </c>
     </row>
     <row r="19" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="29" t="s">
         <v>44</v>
       </c>
       <c r="B19" s="21" t="s">
@@ -2406,10 +2437,10 @@
       <c r="AE19" s="16"/>
       <c r="AF19" s="16"/>
       <c r="AG19" s="17"/>
-      <c r="AH19" s="28"/>
+      <c r="AH19" s="30"/>
     </row>
     <row r="20" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="27"/>
+      <c r="A20" s="29"/>
       <c r="B20" s="21" t="s">
         <v>26</v>
       </c>
@@ -2537,10 +2568,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH20" s="28"/>
+      <c r="AH20" s="30"/>
     </row>
     <row r="21" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="29" t="s">
         <v>45</v>
       </c>
       <c r="B21" s="21" t="s">
@@ -2585,7 +2616,7 @@
       <c r="AH21" s="10"/>
     </row>
     <row r="22" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="27"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="21" t="s">
         <v>26</v>
       </c>
@@ -2719,7 +2750,7 @@
       </c>
     </row>
     <row r="23" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="29" t="s">
         <v>46</v>
       </c>
       <c r="B23" s="21" t="s">
@@ -2761,10 +2792,10 @@
       <c r="AE23" s="16"/>
       <c r="AF23" s="16"/>
       <c r="AG23" s="17"/>
-      <c r="AH23" s="28"/>
+      <c r="AH23" s="30"/>
     </row>
     <row r="24" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="27"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="21" t="s">
         <v>26</v>
       </c>
@@ -2892,10 +2923,10 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AH24" s="28"/>
+      <c r="AH24" s="30"/>
     </row>
     <row r="25" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B25" s="21" t="s">
@@ -2940,7 +2971,7 @@
       <c r="AH25" s="10"/>
     </row>
     <row r="26" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="27"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="21" t="s">
         <v>26</v>
       </c>
@@ -3074,27 +3105,26 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A1:AH1"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="AH7:AH8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="AH11:AH12"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="AH3:AH4"/>
+  <mergeCells count="19">
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="AH23:AH24"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="AH15:AH16"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="AH19:AH20"/>
+    <mergeCell ref="AH13:AH14"/>
+    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AH9:AH10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/REACT-KHACHSAN-VT/public/templates/template-export-excel-thong-ke-phong-da-ban.xlsx
+++ b/REACT-KHACHSAN-VT/public/templates/template-export-excel-thong-ke-phong-da-ban.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\FE-QUANLY-KHACHSAN-VT\REACT-KHACHSAN-VT\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C024809E-AC67-4B89-958D-0ECCA60FC18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D304FA-14EF-4467-84BC-06BE78EB7EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10830" yWindow="3880" windowWidth="25600" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="7" r:id="rId1"/>
@@ -430,7 +430,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -504,12 +504,12 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -519,18 +519,12 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="7" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -541,6 +535,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -870,11 +867,11 @@
       <c r="AH1" s="28"/>
     </row>
     <row r="2" spans="1:34" s="5" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="26" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="25" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="6" t="s">
@@ -979,7 +976,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="22">
-        <f>AVERAGE(D3:AG3)</f>
+        <f>ROUND(AVERAGE(D3:AH3), 0)</f>
         <v>0</v>
       </c>
       <c r="D3" s="14"/>
@@ -1014,7 +1011,7 @@
       <c r="AE3" s="16"/>
       <c r="AF3" s="16"/>
       <c r="AG3" s="17"/>
-      <c r="AH3" s="33"/>
+      <c r="AH3" s="26"/>
     </row>
     <row r="4" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
@@ -1022,7 +1019,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="23">
-        <f>AVERAGE(D4:AG4)</f>
+        <f>AVERAGE(D4:AH4)</f>
         <v>0</v>
       </c>
       <c r="D4" s="18">
@@ -1158,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="22">
-        <f>AVERAGE(D5:AH5)</f>
+        <f>ROUND(AVERAGE(D5:AG5), 0)</f>
         <v>0</v>
       </c>
       <c r="D5" s="9">
@@ -1193,7 +1190,7 @@
       <c r="AE5" s="10"/>
       <c r="AF5" s="10"/>
       <c r="AG5" s="10"/>
-      <c r="AH5" s="34"/>
+      <c r="AH5" s="32"/>
     </row>
     <row r="6" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29"/>
@@ -1201,7 +1198,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="23">
-        <f>AVERAGE(D6:AH6)</f>
+        <f>AVERAGE(D6:AG6)</f>
         <v>0</v>
       </c>
       <c r="D6" s="11">
@@ -1324,7 +1321,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH6" s="35"/>
+      <c r="AH6" s="33"/>
     </row>
     <row r="7" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
@@ -1334,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="22">
-        <f>AVERAGE(D7:AG7)</f>
+        <f>ROUND(AVERAGE(D7:AH7),0)</f>
         <v>0</v>
       </c>
       <c r="D7" s="14"/>
@@ -1369,7 +1366,7 @@
       <c r="AE7" s="16"/>
       <c r="AF7" s="16"/>
       <c r="AG7" s="17"/>
-      <c r="AH7" s="33"/>
+      <c r="AH7" s="26"/>
     </row>
     <row r="8" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="29"/>
@@ -1377,7 +1374,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="23">
-        <f>AVERAGE(D8:AG8)</f>
+        <f>AVERAGE(D8:AH8)</f>
         <v>0</v>
       </c>
       <c r="D8" s="18">
@@ -1513,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="22">
-        <f>AVERAGE(D9:AH9)</f>
+        <f>ROUND(AVERAGE(D9:AG9),0)</f>
         <v>0</v>
       </c>
       <c r="D9" s="9">
@@ -1548,7 +1545,7 @@
       <c r="AE9" s="10"/>
       <c r="AF9" s="10"/>
       <c r="AG9" s="10"/>
-      <c r="AH9" s="36"/>
+      <c r="AH9" s="34"/>
     </row>
     <row r="10" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="29"/>
@@ -1556,7 +1553,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="23">
-        <f>AVERAGE(D10:AH10)</f>
+        <f>AVERAGE(D10:AG10)</f>
         <v>0</v>
       </c>
       <c r="D10" s="11">
@@ -1679,7 +1676,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AH10" s="37"/>
+      <c r="AH10" s="35"/>
     </row>
     <row r="11" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
@@ -1689,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="22">
-        <f>AVERAGE(D11:AG11)</f>
+        <f>ROUND(AVERAGE(D11:AH11),0)</f>
         <v>0</v>
       </c>
       <c r="D11" s="14"/>
@@ -1724,7 +1721,7 @@
       <c r="AE11" s="16"/>
       <c r="AF11" s="16"/>
       <c r="AG11" s="17"/>
-      <c r="AH11" s="33"/>
+      <c r="AH11" s="26"/>
     </row>
     <row r="12" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="29"/>
@@ -1732,7 +1729,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="23">
-        <f>AVERAGE(D12:AG12)</f>
+        <f>AVERAGE(D12:AH12)</f>
         <v>0</v>
       </c>
       <c r="D12" s="18">
@@ -1868,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="22">
-        <f>AVERAGE(D13:AH13)</f>
+        <f>AVERAGE(D13:AG13)</f>
         <v>0</v>
       </c>
       <c r="D13" s="9">
@@ -1903,7 +1900,7 @@
       <c r="AE13" s="10"/>
       <c r="AF13" s="10"/>
       <c r="AG13" s="10"/>
-      <c r="AH13" s="36"/>
+      <c r="AH13" s="34"/>
     </row>
     <row r="14" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="29"/>
@@ -1911,7 +1908,7 @@
         <v>26</v>
       </c>
       <c r="C14" s="23">
-        <f>AVERAGE(D14:AH14)</f>
+        <f>AVERAGE(D14:AG14)</f>
         <v>0</v>
       </c>
       <c r="D14" s="11">
@@ -2034,7 +2031,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH14" s="37"/>
+      <c r="AH14" s="35"/>
     </row>
     <row r="15" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
@@ -2044,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="22">
-        <f>AVERAGE(D15:AG15)</f>
+        <f>ROUND(AVERAGE(D15:AH15),0)</f>
         <v>0</v>
       </c>
       <c r="D15" s="14"/>
@@ -2079,7 +2076,7 @@
       <c r="AE15" s="16"/>
       <c r="AF15" s="16"/>
       <c r="AG15" s="17"/>
-      <c r="AH15" s="33"/>
+      <c r="AH15" s="26"/>
     </row>
     <row r="16" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="29"/>
@@ -2087,7 +2084,7 @@
         <v>26</v>
       </c>
       <c r="C16" s="23">
-        <f>AVERAGE(D16:AG16)</f>
+        <f>AVERAGE(D16:AH16)</f>
         <v>0</v>
       </c>
       <c r="D16" s="18">
@@ -2223,7 +2220,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="22">
-        <f>AVERAGE(D17:AH17)</f>
+        <f>ROUND(AVERAGE(D17:AH17),0)</f>
         <v>0</v>
       </c>
       <c r="D17" s="9">
@@ -2402,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="22">
-        <f>AVERAGE(D19:AG19)</f>
+        <f>ROUND(AVERAGE(D19:AG19),0)</f>
         <v>0</v>
       </c>
       <c r="D19" s="14"/>
@@ -2437,14 +2434,14 @@
       <c r="AE19" s="16"/>
       <c r="AF19" s="16"/>
       <c r="AG19" s="17"/>
-      <c r="AH19" s="30"/>
+      <c r="AH19" s="36"/>
     </row>
     <row r="20" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="29"/>
       <c r="B20" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="23">
         <f>AVERAGE(D20:AG20)</f>
         <v>0</v>
       </c>
@@ -2568,7 +2565,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH20" s="30"/>
+      <c r="AH20" s="36"/>
     </row>
     <row r="21" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="29" t="s">
@@ -2578,7 +2575,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="22">
-        <f>AVERAGE(D21:AH21)</f>
+        <f>ROUND(AVERAGE(D21:AH21),0)</f>
         <v>0</v>
       </c>
       <c r="D21" s="9">
@@ -2757,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="22">
-        <f>AVERAGE(D23:AG23)</f>
+        <f>ROUND(AVERAGE(D23:AG23),0)</f>
         <v>0</v>
       </c>
       <c r="D23" s="14"/>
@@ -2792,7 +2789,7 @@
       <c r="AE23" s="16"/>
       <c r="AF23" s="16"/>
       <c r="AG23" s="17"/>
-      <c r="AH23" s="30"/>
+      <c r="AH23" s="36"/>
     </row>
     <row r="24" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="29"/>
@@ -2923,7 +2920,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AH24" s="30"/>
+      <c r="AH24" s="36"/>
     </row>
     <row r="25" spans="1:34" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="29" t="s">
@@ -2933,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="22">
-        <f>AVERAGE(D25:AH25)</f>
+        <f>ROUND(AVERAGE(D25:AH25),0)</f>
         <v>0</v>
       </c>
       <c r="D25" s="9">
